--- a/R Markdown/resultados/tabelas_25_DA/regionalizacao_acoes_2025_25_DA.xlsx
+++ b/R Markdown/resultados/tabelas_25_DA/regionalizacao_acoes_2025_25_DA.xlsx
@@ -1,21 +1,378 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cloudprodamazhotmail-my.sharepoint.com/personal/gabrielmachado_prefeitura_sp_gov_br/Documents/Área de Trabalho/IDRGP/IDRGP-2025/R Markdown/resultados/tabelas_25_DA/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_B40CFCD28F79A8D366075C52F37BD272CA428E04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{143F3EC0-6ED2-4613-B143-789870D3A87D}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView minimized="1" xWindow="5130" yWindow="690" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
+  <si>
+    <t>ano</t>
+  </si>
+  <si>
+    <t>codigo_proj_ativ</t>
+  </si>
+  <si>
+    <t>descricao_proj_ativ</t>
+  </si>
+  <si>
+    <t>valor_total</t>
+  </si>
+  <si>
+    <t>valor_regionalizado</t>
+  </si>
+  <si>
+    <t>n_subpref</t>
+  </si>
+  <si>
+    <t>perc_regionalizado</t>
+  </si>
+  <si>
+    <t>1170</t>
+  </si>
+  <si>
+    <t>Intervenção, Urbanização e Melhoria de Bairros - Plano de Obras das Subprefeituras</t>
+  </si>
+  <si>
+    <t>1193</t>
+  </si>
+  <si>
+    <t>Obras e Serviços nas Áreas de Riscos Geológicos - Preventivas</t>
+  </si>
+  <si>
+    <t>1276</t>
+  </si>
+  <si>
+    <t>Projetos e Ações de Apoio Habitacional</t>
+  </si>
+  <si>
+    <t>1525</t>
+  </si>
+  <si>
+    <t>Construção e Implantação de Equipamentos de Atenção Básica e Especialidades</t>
+  </si>
+  <si>
+    <t>1526</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Equipamentos de Atenção Básica e Especialidades</t>
+  </si>
+  <si>
+    <t>1530</t>
+  </si>
+  <si>
+    <t>Construção e Implantação de Equipamentos de Saúde Animal</t>
+  </si>
+  <si>
+    <t>1535</t>
+  </si>
+  <si>
+    <t>Construção e Implantação de Equipamentos em Atenção Hospitalar e de Urgência e Emergência</t>
+  </si>
+  <si>
+    <t>1536</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Equipamentos em Atenção Hospitalar e de Urgência e Emergência</t>
+  </si>
+  <si>
+    <t>1702</t>
+  </si>
+  <si>
+    <t>Construção e Implantação de Parques Urbanos e Lineares</t>
+  </si>
+  <si>
+    <t>1703</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Parques Urbanos e Lineares</t>
+  </si>
+  <si>
+    <t>1896</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Clube da Comunidade (CDC)</t>
+  </si>
+  <si>
+    <t>2410</t>
+  </si>
+  <si>
+    <t>Fomento e Apoio ao Cooperativismo</t>
+  </si>
+  <si>
+    <t>2416</t>
+  </si>
+  <si>
+    <t>Qualificação Profissional e Empreendedora</t>
+  </si>
+  <si>
+    <t>2635</t>
+  </si>
+  <si>
+    <t>Serviço de Moradia Transitória</t>
+  </si>
+  <si>
+    <t>3340</t>
+  </si>
+  <si>
+    <t>Programa Pode Entrar</t>
+  </si>
+  <si>
+    <t>3350</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Áreas Públicas</t>
+  </si>
+  <si>
+    <t>3353</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Unidades Habitacionais</t>
+  </si>
+  <si>
+    <t>3354</t>
+  </si>
+  <si>
+    <t>Construção de Unidades Habitacionais</t>
+  </si>
+  <si>
+    <t>3355</t>
+  </si>
+  <si>
+    <t>Execução do Programa de Mananciais</t>
+  </si>
+  <si>
+    <t>3356</t>
+  </si>
+  <si>
+    <t>Regularização Fundiária</t>
+  </si>
+  <si>
+    <t>3357</t>
+  </si>
+  <si>
+    <t>Urbanização de Favelas</t>
+  </si>
+  <si>
+    <t>3358</t>
+  </si>
+  <si>
+    <t>Locação Social</t>
+  </si>
+  <si>
+    <t>3359</t>
+  </si>
+  <si>
+    <t>Construção de Centros de Educação Infantil - CEI</t>
+  </si>
+  <si>
+    <t>3360</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Centros de Educação Infantil (CEI)</t>
+  </si>
+  <si>
+    <t>3361</t>
+  </si>
+  <si>
+    <t>Construção de Escolas Municipais de Educação Infantil (EMEI)</t>
+  </si>
+  <si>
+    <t>3362</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Escolas Municipais de Educação Infantil (EMEI)</t>
+  </si>
+  <si>
+    <t>3363</t>
+  </si>
+  <si>
+    <t>Construção e Implantação de Centros Educacionais Unificados (CEU)</t>
+  </si>
+  <si>
+    <t>3364</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Centros Educacionais Unificados (CEU)</t>
+  </si>
+  <si>
+    <t>3365</t>
+  </si>
+  <si>
+    <t>Construção de Escolas Municipais de Ensino Fundamental (EMEF)</t>
+  </si>
+  <si>
+    <t>3366</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Escola Municipal de Ensino Fundamental (EMEF)</t>
+  </si>
+  <si>
+    <t>3512</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Equipamentos Esportivos</t>
+  </si>
+  <si>
+    <t>3664</t>
+  </si>
+  <si>
+    <t>Urbanismo Social</t>
+  </si>
+  <si>
+    <t>3757</t>
+  </si>
+  <si>
+    <t>Implantação de Projetos de Redesenho Urbano para Segurança Viária</t>
+  </si>
+  <si>
+    <t>4302</t>
+  </si>
+  <si>
+    <t>Armazém Solidário</t>
+  </si>
+  <si>
+    <t>4318</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações para Juventude</t>
+  </si>
+  <si>
+    <t>4319</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações Inclusivas</t>
+  </si>
+  <si>
+    <t>4320</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações para Pessoa Idosa</t>
+  </si>
+  <si>
+    <t>4321</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações para a População em Situação de Rua</t>
+  </si>
+  <si>
+    <t>4322</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações para Povos Indígenas</t>
+  </si>
+  <si>
+    <t>4324</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações para Imigrantes e Promoção ao Trabalho Decente</t>
+  </si>
+  <si>
+    <t>4327</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações para Promoção da Igualdade Racial</t>
+  </si>
+  <si>
+    <t>4328</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações Para Criança e Adolescente</t>
+  </si>
+  <si>
+    <t>4329</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações para Mulheres</t>
+  </si>
+  <si>
+    <t>4340</t>
+  </si>
+  <si>
+    <t>Ações Integradas de Segurança Pública - Operação Delegada - Convênio SSP SO</t>
+  </si>
+  <si>
+    <t>4424</t>
+  </si>
+  <si>
+    <t>Fomento às Cadeias Produtivas, Vocações Produtivas e Projetos Locais</t>
+  </si>
+  <si>
+    <t>4426</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações de Subsistência, Segurança Alimentar e Nutricional</t>
+  </si>
+  <si>
+    <t>5204</t>
+  </si>
+  <si>
+    <t>Avança Saúde SP - Ampliação, Reforma e Requalificação de Equipamentos de Saúde</t>
+  </si>
+  <si>
+    <t>5207</t>
+  </si>
+  <si>
+    <t>BID II - Ampliação, Reforma e Requalificação de Equipamentos de Assistência Hospitalar</t>
+  </si>
+  <si>
+    <t>5407</t>
+  </si>
+  <si>
+    <t>Centro Municipal para Pessoas com Transtorno do Espectro Autista</t>
+  </si>
+  <si>
+    <t>5960</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Equipamentos Culturais</t>
+  </si>
+  <si>
+    <t>6160</t>
+  </si>
+  <si>
+    <t>Ações Permanentes de Promoção dos Direitos da Criança e do Adolescente</t>
+  </si>
+  <si>
+    <t>7110</t>
+  </si>
+  <si>
+    <t>Projetos para Inclusão da Pessoa com Deficiência</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +420,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +472,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +506,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +541,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,60 +717,47 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="3" max="3" width="84" customWidth="1"/>
+    <col min="6" max="6" width="38.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>codigo_proj_ativ</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>descricao_proj_ativ</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>valor_total</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>valor_regionalizado</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>n_subpref</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>perc_regionalizado</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2025</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1170</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Intervenção, Urbanização e Melhoria de Bairros - Plano de Obras das Subprefeituras</t>
-        </is>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -415,19 +769,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2025</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1193</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Obras e Serviços nas Áreas de Riscos Geológicos - Preventivas</t>
-        </is>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -439,19 +789,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2025</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1276</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Projetos e Ações de Apoio Habitacional</t>
-        </is>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -463,19 +809,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2025</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1525</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Construção e Implantação de Equipamentos de Atenção Básica e Especialidades</t>
-        </is>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -487,19 +829,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2025</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1526</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Equipamentos de Atenção Básica e Especialidades</t>
-        </is>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -511,19 +849,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2025</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1530</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Construção e Implantação de Equipamentos de Saúde Animal</t>
-        </is>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -535,19 +869,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2025</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1535</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Construção e Implantação de Equipamentos em Atenção Hospitalar e de Urgência e Emergência</t>
-        </is>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -559,19 +889,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2025</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1536</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Equipamentos em Atenção Hospitalar e de Urgência e Emergência</t>
-        </is>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -583,19 +909,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2025</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1702</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Construção e Implantação de Parques Urbanos e Lineares</t>
-        </is>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -607,19 +929,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2025</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1703</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Parques Urbanos e Lineares</t>
-        </is>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>26</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -631,19 +949,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2025</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1896</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Clube da Comunidade (CDC)</t>
-        </is>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -655,19 +969,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2025</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2410</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Fomento e Apoio ao Cooperativismo</t>
-        </is>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -679,19 +989,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2025</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2416</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Qualificação Profissional e Empreendedora</t>
-        </is>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>32</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -703,19 +1009,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2025</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2635</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Serviço de Moradia Transitória</t>
-        </is>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>34</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -727,19 +1029,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2025</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3340</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Programa Pode Entrar</t>
-        </is>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>36</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -751,19 +1049,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2025</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3350</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Áreas Públicas</t>
-        </is>
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
+        <v>38</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -775,19 +1069,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2025</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3353</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Unidades Habitacionais</t>
-        </is>
+      <c r="B18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" t="s">
+        <v>40</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -799,19 +1089,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2025</v>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3354</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Construção de Unidades Habitacionais</t>
-        </is>
+      <c r="B19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" t="s">
+        <v>42</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -823,19 +1109,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2025</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3355</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Execução do Programa de Mananciais</t>
-        </is>
+      <c r="B20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" t="s">
+        <v>44</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -847,19 +1129,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2025</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3356</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Regularização Fundiária</t>
-        </is>
+      <c r="B21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" t="s">
+        <v>46</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -871,19 +1149,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2025</v>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3357</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Urbanização de Favelas</t>
-        </is>
+      <c r="B22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" t="s">
+        <v>48</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -895,19 +1169,15 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2025</v>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3358</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Locação Social</t>
-        </is>
+      <c r="B23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" t="s">
+        <v>50</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -919,19 +1189,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2025</v>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3359</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Construção de Centros de Educação Infantil - CEI</t>
-        </is>
+      <c r="B24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" t="s">
+        <v>52</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -943,19 +1209,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2025</v>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3360</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Centros de Educação Infantil (CEI)</t>
-        </is>
+      <c r="B25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" t="s">
+        <v>54</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -967,19 +1229,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2025</v>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3361</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Construção de Escolas Municipais de Educação Infantil (EMEI)</t>
-        </is>
+      <c r="B26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" t="s">
+        <v>56</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -991,19 +1249,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2025</v>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3362</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Escolas Municipais de Educação Infantil (EMEI)</t>
-        </is>
+      <c r="B27" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" t="s">
+        <v>58</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1015,19 +1269,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2025</v>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3363</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Construção e Implantação de Centros Educacionais Unificados (CEU)</t>
-        </is>
+      <c r="B28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" t="s">
+        <v>60</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1039,19 +1289,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2025</v>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3364</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Centros Educacionais Unificados (CEU)</t>
-        </is>
+      <c r="B29" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" t="s">
+        <v>62</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1063,19 +1309,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2025</v>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3365</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Construção de Escolas Municipais de Ensino Fundamental (EMEF)</t>
-        </is>
+      <c r="B30" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" t="s">
+        <v>64</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1087,19 +1329,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2025</v>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3366</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Escola Municipal de Ensino Fundamental (EMEF)</t>
-        </is>
+      <c r="B31" t="s">
+        <v>65</v>
+      </c>
+      <c r="C31" t="s">
+        <v>66</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1111,19 +1349,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2025</v>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3512</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Equipamentos Esportivos</t>
-        </is>
+      <c r="B32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" t="s">
+        <v>68</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -1135,19 +1369,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2025</v>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3664</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Urbanismo Social</t>
-        </is>
+      <c r="B33" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" t="s">
+        <v>70</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -1159,19 +1389,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2025</v>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3757</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Implantação de Projetos de Redesenho Urbano para Segurança Viária</t>
-        </is>
+      <c r="B34" t="s">
+        <v>71</v>
+      </c>
+      <c r="C34" t="s">
+        <v>72</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -1183,19 +1409,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2025</v>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4302</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Armazém Solidário</t>
-        </is>
+      <c r="B35" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" t="s">
+        <v>74</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -1207,19 +1429,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2025</v>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>4318</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações para Juventude</t>
-        </is>
+      <c r="B36" t="s">
+        <v>75</v>
+      </c>
+      <c r="C36" t="s">
+        <v>76</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -1231,19 +1449,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2025</v>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>4319</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações Inclusivas</t>
-        </is>
+      <c r="B37" t="s">
+        <v>77</v>
+      </c>
+      <c r="C37" t="s">
+        <v>78</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -1255,19 +1469,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2025</v>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>4320</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações para Pessoa Idosa</t>
-        </is>
+      <c r="B38" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" t="s">
+        <v>80</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -1279,19 +1489,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2025</v>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>4321</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações para a População em Situação de Rua</t>
-        </is>
+      <c r="B39" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" t="s">
+        <v>82</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -1303,19 +1509,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2025</v>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>4322</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações para Povos Indígenas</t>
-        </is>
+      <c r="B40" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" t="s">
+        <v>84</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -1327,19 +1529,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2025</v>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>4324</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações para Imigrantes e Promoção ao Trabalho Decente</t>
-        </is>
+      <c r="B41" t="s">
+        <v>85</v>
+      </c>
+      <c r="C41" t="s">
+        <v>86</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -1351,19 +1549,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2025</v>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>4327</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações para Promoção da Igualdade Racial</t>
-        </is>
+      <c r="B42" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" t="s">
+        <v>88</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -1375,19 +1569,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2025</v>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>4328</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações Para Criança e Adolescente</t>
-        </is>
+      <c r="B43" t="s">
+        <v>89</v>
+      </c>
+      <c r="C43" t="s">
+        <v>90</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -1399,19 +1589,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2025</v>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>4329</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações para Mulheres</t>
-        </is>
+      <c r="B44" t="s">
+        <v>91</v>
+      </c>
+      <c r="C44" t="s">
+        <v>92</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -1423,19 +1609,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2025</v>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>4340</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ações Integradas de Segurança Pública - Operação Delegada - Convênio SSP SO</t>
-        </is>
+      <c r="B45" t="s">
+        <v>93</v>
+      </c>
+      <c r="C45" t="s">
+        <v>94</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -1447,19 +1629,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2025</v>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>4424</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Fomento às Cadeias Produtivas, Vocações Produtivas e Projetos Locais</t>
-        </is>
+      <c r="B46" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46" t="s">
+        <v>96</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -1471,19 +1649,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2025</v>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>4426</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações de Subsistência, Segurança Alimentar e Nutricional</t>
-        </is>
+      <c r="B47" t="s">
+        <v>97</v>
+      </c>
+      <c r="C47" t="s">
+        <v>98</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -1495,19 +1669,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2025</v>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>5204</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Avança Saúde SP - Ampliação, Reforma e Requalificação de Equipamentos de Saúde</t>
-        </is>
+      <c r="B48" t="s">
+        <v>99</v>
+      </c>
+      <c r="C48" t="s">
+        <v>100</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -1519,19 +1689,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2025</v>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>5207</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>BID II - Ampliação, Reforma e Requalificação de Equipamentos de Assistência Hospitalar</t>
-        </is>
+      <c r="B49" t="s">
+        <v>101</v>
+      </c>
+      <c r="C49" t="s">
+        <v>102</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -1543,19 +1709,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2025</v>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>5407</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Centro Municipal para Pessoas com Transtorno do Espectro Autista</t>
-        </is>
+      <c r="B50" t="s">
+        <v>103</v>
+      </c>
+      <c r="C50" t="s">
+        <v>104</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -1567,19 +1729,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2025</v>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>5960</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Equipamentos Culturais</t>
-        </is>
+      <c r="B51" t="s">
+        <v>105</v>
+      </c>
+      <c r="C51" t="s">
+        <v>106</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -1591,19 +1749,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2025</v>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>6160</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ações Permanentes de Promoção dos Direitos da Criança e do Adolescente</t>
-        </is>
+      <c r="B52" t="s">
+        <v>107</v>
+      </c>
+      <c r="C52" t="s">
+        <v>108</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -1615,19 +1769,15 @@
         <v>29</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2025</v>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>7110</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Projetos para Inclusão da Pessoa com Deficiência</t>
-        </is>
+      <c r="B53" t="s">
+        <v>109</v>
+      </c>
+      <c r="C53" t="s">
+        <v>110</v>
       </c>
       <c r="D53">
         <v>0</v>
